--- a/data/config/luban/config/general/building.xlsx
+++ b/data/config/luban/config/general/building.xlsx
@@ -7,10 +7,10 @@
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Building" sheetId="1" r:id="rId1"/>
+    <sheet name="building" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Building!$A$3:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">building!$A$3:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/config/luban/config/general/building.xlsx
+++ b/data/config/luban/config/general/building.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -56,6 +56,9 @@
     <t xml:space="preserve">produce_multiplying </t>
   </si>
   <si>
+    <t>frequency</t>
+  </si>
+  <si>
     <t>icon_res</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>产出倍率</t>
+  </si>
+  <si>
+    <t>产出频率（毫秒）</t>
   </si>
   <si>
     <t>小图资源路径</t>
@@ -1337,7 +1343,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1345,15 +1351,16 @@
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="2" customWidth="1"/>
     <col min="5" max="8" width="12.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="37.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.125" style="2" customWidth="1"/>
-    <col min="11" max="12" width="25.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="27.125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="17.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="37.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.125" style="2" customWidth="1"/>
+    <col min="12" max="13" width="25.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="27.125" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1396,98 +1403,107 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>20</v>
+      <c r="O2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:14">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="B4" s="2">
         <v>9011001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2">
         <f>IF(B4="","",MOD(INT(B4/1000),10))</f>
@@ -1506,23 +1522,26 @@
       <c r="H4" s="2">
         <v>100</v>
       </c>
-      <c r="I4" s="2" t="str">
+      <c r="I4" s="2">
+        <v>6000</v>
+      </c>
+      <c r="J4" s="2" t="str">
         <f>"Assets/Game/Textures/Building/"&amp;B4&amp;".png"</f>
         <v>Assets/Game/Textures/Building/9011001.png</v>
       </c>
-      <c r="K4" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="L4" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="M4" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="B5" s="2">
         <v>9021002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2">
         <f>IF(B5="","",MOD(INT(B5/1000),10))</f>
@@ -1541,23 +1560,26 @@
       <c r="H5" s="2">
         <v>80</v>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="I5" s="2">
+        <v>6000</v>
+      </c>
+      <c r="J5" s="2" t="str">
         <f>"Assets/Game/Textures/Building/"&amp;B5&amp;".png"</f>
         <v>Assets/Game/Textures/Building/9021002.png</v>
       </c>
-      <c r="K5" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="L5" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="M5" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="B6" s="2">
         <v>9031003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2">
         <f>IF(B6="","",MOD(INT(B6/1000),10))</f>
@@ -1576,23 +1598,26 @@
       <c r="H6" s="2">
         <v>70</v>
       </c>
-      <c r="I6" s="2" t="str">
+      <c r="I6" s="2">
+        <v>6000</v>
+      </c>
+      <c r="J6" s="2" t="str">
         <f>"Assets/Game/Textures/Building/"&amp;B6&amp;".png"</f>
         <v>Assets/Game/Textures/Building/9031003.png</v>
       </c>
-      <c r="K6" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="L6" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="M6" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="B7" s="2">
         <v>9041004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2">
         <f>IF(B7="","",MOD(INT(B7/1000),10))</f>
@@ -1611,23 +1636,26 @@
       <c r="H7" s="2">
         <v>60</v>
       </c>
-      <c r="I7" s="2" t="str">
+      <c r="I7" s="2">
+        <v>6000</v>
+      </c>
+      <c r="J7" s="2" t="str">
         <f>"Assets/Game/Textures/Building/"&amp;B7&amp;".png"</f>
         <v>Assets/Game/Textures/Building/9041004.png</v>
       </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="L7" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="M7" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="B8" s="2">
         <v>9051005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2">
         <f>IF(B8="","",MOD(INT(B8/1000),10))</f>
@@ -1640,14 +1668,14 @@
       <c r="F8" s="2">
         <v>1001003</v>
       </c>
-      <c r="I8" s="2" t="str">
+      <c r="J8" s="2" t="str">
         <f>"Assets/Game/Textures/Building/"&amp;B8&amp;".png"</f>
         <v>Assets/Game/Textures/Building/9051005.png</v>
       </c>
-      <c r="K8" s="2" t="b">
+      <c r="L8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L8" s="2" t="b">
+      <c r="M8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
